--- a/data/trans_dic/P55$familiarvive-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 28,01</t>
+          <t>5,46; 28,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 31,52</t>
+          <t>3,52; 32,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 27,56</t>
+          <t>2,91; 27,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,51</t>
+          <t>0,82; 8,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,49; 41,88</t>
+          <t>14,32; 42,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 28,94</t>
+          <t>9,05; 31,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 36,69</t>
+          <t>12,18; 37,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 25,21</t>
+          <t>13,08; 24,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,33; 31,81</t>
+          <t>13,74; 32,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,51; 25,87</t>
+          <t>9,48; 25,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 29,14</t>
+          <t>11,16; 28,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 16,82</t>
+          <t>9,08; 16,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 28,87</t>
+          <t>8,07; 28,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 27,02</t>
+          <t>6,63; 28,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 28,22</t>
+          <t>6,44; 27,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 17,07</t>
+          <t>3,08; 16,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 41,4</t>
+          <t>18,1; 41,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,03; 43,06</t>
+          <t>21,76; 42,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,57; 40,51</t>
+          <t>18,13; 41,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,14; 25,25</t>
+          <t>13,3; 25,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,4; 32,02</t>
+          <t>16,23; 33,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,69; 34,66</t>
+          <t>18,72; 34,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,5; 32,91</t>
+          <t>16,0; 33,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 20,73</t>
+          <t>11,48; 21,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 45,83</t>
+          <t>4,68; 44,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 45,74</t>
+          <t>7,92; 47,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,14; 42,19</t>
+          <t>10,52; 45,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 35,87</t>
+          <t>8,64; 35,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 36,14</t>
+          <t>10,84; 35,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,91; 52,54</t>
+          <t>24,29; 52,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,95; 46,59</t>
+          <t>17,4; 45,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 35,87</t>
+          <t>18,04; 35,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 35,3</t>
+          <t>12,32; 32,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,29; 45,41</t>
+          <t>22,6; 45,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 40,52</t>
+          <t>18,13; 40,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 32,25</t>
+          <t>17,5; 31,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 27,95</t>
+          <t>3,41; 28,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 39,96</t>
+          <t>10,92; 43,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 30,99</t>
+          <t>4,79; 32,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 28,05</t>
+          <t>9,29; 27,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,37; 51,67</t>
+          <t>29,55; 52,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,48; 39,58</t>
+          <t>19,0; 39,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 37,17</t>
+          <t>14,21; 35,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 25,17</t>
+          <t>13,89; 23,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,93; 42,89</t>
+          <t>24,14; 43,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,76; 36,27</t>
+          <t>19,3; 35,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,67; 29,9</t>
+          <t>13,04; 30,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,36; 23,24</t>
+          <t>13,6; 22,92</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 22,41</t>
+          <t>9,94; 22,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 26,09</t>
+          <t>11,84; 25,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 21,32</t>
+          <t>9,96; 22,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,23</t>
+          <t>7,05; 14,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,77; 37,24</t>
+          <t>24,37; 37,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,72; 35,4</t>
+          <t>23,57; 34,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,64; 33,14</t>
+          <t>20,8; 32,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,88; 23,33</t>
+          <t>17,17; 23,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,76; 29,66</t>
+          <t>20,75; 30,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 29,7</t>
+          <t>21,27; 29,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,0; 28,01</t>
+          <t>18,81; 27,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,64</t>
+          <t>14,67; 19,82</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1866; 9487</t>
+          <t>1851; 9713</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1169; 10257</t>
+          <t>1144; 10474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>952; 7656</t>
+          <t>807; 7585</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>418; 4719</t>
+          <t>406; 4412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6040; 18755</t>
+          <t>6412; 18811</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5610; 17655</t>
+          <t>5523; 19205</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7508; 22063</t>
+          <t>7327; 22558</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10778; 20087</t>
+          <t>10422; 19576</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10489; 25025</t>
+          <t>10807; 25400</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8899; 24196</t>
+          <t>8871; 23400</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10459; 25617</t>
+          <t>9815; 25273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11782; 21745</t>
+          <t>11740; 21910</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3897; 13864</t>
+          <t>3876; 13799</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2199; 12338</t>
+          <t>3025; 12865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2671; 11543</t>
+          <t>2633; 11300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1053; 6606</t>
+          <t>1193; 6531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12154; 28017</t>
+          <t>12252; 28042</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19464; 38038</t>
+          <t>19222; 37359</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14267; 31126</t>
+          <t>13928; 31965</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11296; 21710</t>
+          <t>11435; 21864</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17819; 37053</t>
+          <t>18778; 38240</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25038; 46444</t>
+          <t>25078; 46446</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19431; 38755</t>
+          <t>18837; 39100</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14346; 25850</t>
+          <t>14316; 26328</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1621; 9888</t>
+          <t>1009; 9513</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2187; 12779</t>
+          <t>2212; 13178</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1894; 9815</t>
+          <t>2446; 10509</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1930; 9156</t>
+          <t>2205; 9008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5132; 16793</t>
+          <t>5039; 16524</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12414; 27276</t>
+          <t>12610; 27467</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8743; 24027</t>
+          <t>8972; 23625</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10569; 20917</t>
+          <t>10519; 20849</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8106; 24021</t>
+          <t>8381; 22169</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17798; 36264</t>
+          <t>18044; 36664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13456; 30320</t>
+          <t>13568; 30388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14310; 27034</t>
+          <t>14669; 26714</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>813; 6458</t>
+          <t>787; 6646</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4427; 15998</t>
+          <t>4371; 17336</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1338; 9145</t>
+          <t>1413; 9546</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3829; 12125</t>
+          <t>4017; 11929</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20425; 37197</t>
+          <t>21271; 37864</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14461; 30984</t>
+          <t>14872; 31250</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10895; 29291</t>
+          <t>11198; 28223</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14570; 26239</t>
+          <t>14484; 24990</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22754; 40784</t>
+          <t>22956; 41322</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22195; 42905</t>
+          <t>22833; 42227</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13725; 32390</t>
+          <t>14119; 33292</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19707; 34273</t>
+          <t>20058; 33806</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12488; 28367</t>
+          <t>12583; 28630</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17908; 38132</t>
+          <t>17303; 37958</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11466; 25897</t>
+          <t>12101; 26920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11495; 23915</t>
+          <t>11073; 23212</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57205; 85990</t>
+          <t>56279; 85605</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66306; 98944</t>
+          <t>65884; 96460</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55186; 88615</t>
+          <t>55599; 86891</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55413; 76583</t>
+          <t>56376; 76944</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74219; 106044</t>
+          <t>74176; 108128</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89589; 126445</t>
+          <t>90556; 126274</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70004; 108901</t>
+          <t>73146; 108127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69807; 95337</t>
+          <t>71176; 96198</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$familiarvive-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 28,67</t>
+          <t>5,4; 28,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 32,19</t>
+          <t>3,38; 30,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 27,3</t>
+          <t>2,88; 27,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,89</t>
+          <t>0,8; 8,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 42,0</t>
+          <t>15,06; 42,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,05; 31,48</t>
+          <t>9,2; 30,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 37,51</t>
+          <t>11,78; 35,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 24,57</t>
+          <t>12,78; 24,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,74; 32,29</t>
+          <t>13,35; 31,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 25,02</t>
+          <t>9,55; 26,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 28,75</t>
+          <t>11,46; 29,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,95</t>
+          <t>8,34; 16,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 28,74</t>
+          <t>7,87; 28,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 28,18</t>
+          <t>6,77; 29,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 27,62</t>
+          <t>6,29; 26,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 16,88</t>
+          <t>3,54; 18,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,1; 41,43</t>
+          <t>18,77; 42,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,76; 42,29</t>
+          <t>21,79; 42,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 41,6</t>
+          <t>18,72; 41,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 25,42</t>
+          <t>13,94; 26,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,23; 33,05</t>
+          <t>15,4; 32,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,72; 34,66</t>
+          <t>18,08; 34,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,0; 33,21</t>
+          <t>16,43; 34,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 21,11</t>
+          <t>11,68; 21,82</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 44,09</t>
+          <t>4,66; 44,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 47,16</t>
+          <t>7,89; 46,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,52; 45,18</t>
+          <t>10,34; 42,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 35,29</t>
+          <t>8,59; 35,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 35,56</t>
+          <t>10,24; 36,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,29; 52,91</t>
+          <t>24,12; 52,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,4; 45,81</t>
+          <t>17,19; 45,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 35,76</t>
+          <t>17,69; 35,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 32,58</t>
+          <t>12,59; 32,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,6; 45,91</t>
+          <t>22,61; 44,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 40,61</t>
+          <t>17,79; 41,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,5; 31,86</t>
+          <t>17,69; 32,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 28,76</t>
+          <t>3,5; 29,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,92; 43,3</t>
+          <t>10,75; 43,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 32,35</t>
+          <t>3,53; 30,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 27,59</t>
+          <t>8,51; 26,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,55; 52,59</t>
+          <t>28,46; 53,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,0; 39,92</t>
+          <t>18,58; 39,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,21; 35,81</t>
+          <t>13,79; 35,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,89; 23,97</t>
+          <t>12,88; 24,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,14; 43,45</t>
+          <t>23,98; 43,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 35,69</t>
+          <t>19,84; 36,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 30,74</t>
+          <t>13,02; 30,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 22,92</t>
+          <t>13,61; 22,67</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 22,62</t>
+          <t>9,86; 22,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,84; 25,97</t>
+          <t>12,08; 26,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,96; 22,16</t>
+          <t>9,5; 21,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 14,78</t>
+          <t>7,33; 15,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,37; 37,07</t>
+          <t>24,39; 36,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,57; 34,51</t>
+          <t>23,66; 35,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,8; 32,5</t>
+          <t>21,34; 33,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 23,44</t>
+          <t>16,98; 23,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,75; 30,25</t>
+          <t>20,76; 30,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,27; 29,66</t>
+          <t>21,13; 29,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,81; 27,81</t>
+          <t>18,6; 27,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,82</t>
+          <t>15,06; 20,0</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>17257</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1851; 9713</t>
+          <t>1831; 9488</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1144; 10474</t>
+          <t>1101; 9861</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>807; 7585</t>
+          <t>801; 7653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>406; 4412</t>
+          <t>421; 4470</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6412; 18811</t>
+          <t>6745; 19221</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5523; 19205</t>
+          <t>5613; 18891</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7327; 22558</t>
+          <t>7084; 21123</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10422; 19576</t>
+          <t>10851; 20760</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10807; 25400</t>
+          <t>10503; 24812</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8871; 23400</t>
+          <t>8934; 25055</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9815; 25273</t>
+          <t>10073; 25574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11740; 21910</t>
+          <t>11505; 22815</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16509</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>22280</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3876; 13799</t>
+          <t>3780; 13712</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3025; 12865</t>
+          <t>3093; 13277</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2633; 11300</t>
+          <t>2575; 10854</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1193; 6531</t>
+          <t>1482; 7848</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12252; 28042</t>
+          <t>12707; 28935</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19222; 37359</t>
+          <t>19251; 37438</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13928; 31965</t>
+          <t>14383; 31823</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11435; 21864</t>
+          <t>13191; 25091</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18778; 38240</t>
+          <t>17816; 37589</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25078; 46446</t>
+          <t>24227; 45930</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18837; 39100</t>
+          <t>19349; 40224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14316; 26328</t>
+          <t>15936; 29777</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20147</t>
+          <t>23054</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1009; 9513</t>
+          <t>1005; 9629</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2212; 13178</t>
+          <t>2204; 13093</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2446; 10509</t>
+          <t>2406; 9990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2205; 9008</t>
+          <t>2552; 10518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5039; 16524</t>
+          <t>4760; 17083</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12610; 27467</t>
+          <t>12521; 27351</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8972; 23625</t>
+          <t>8864; 23375</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10519; 20849</t>
+          <t>11481; 23260</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8381; 22169</t>
+          <t>8567; 22408</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18044; 36664</t>
+          <t>18059; 35888</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13568; 30388</t>
+          <t>13314; 30696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14669; 26714</t>
+          <t>16735; 30715</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>27811</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>787; 6646</t>
+          <t>808; 6739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4371; 17336</t>
+          <t>4304; 17284</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1413; 9546</t>
+          <t>1042; 9001</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4017; 11929</t>
+          <t>3791; 11606</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21271; 37864</t>
+          <t>20487; 38163</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14872; 31250</t>
+          <t>14546; 31300</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11198; 28223</t>
+          <t>10867; 28022</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14484; 24990</t>
+          <t>14537; 27921</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22956; 41322</t>
+          <t>22808; 41727</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22833; 42227</t>
+          <t>23474; 42973</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14119; 33292</t>
+          <t>14102; 32860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20058; 33806</t>
+          <t>21422; 35678</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>65663</t>
+          <t>71918</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82643</t>
+          <t>90402</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12583; 28630</t>
+          <t>12479; 28676</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17303; 37958</t>
+          <t>17651; 38661</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12101; 26920</t>
+          <t>11535; 26314</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11073; 23212</t>
+          <t>12401; 25873</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56279; 85605</t>
+          <t>56317; 84259</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65884; 96460</t>
+          <t>66146; 98151</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55599; 86891</t>
+          <t>57053; 88563</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>56376; 76944</t>
+          <t>60645; 84124</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74176; 108128</t>
+          <t>74223; 108590</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90556; 126274</t>
+          <t>89947; 126573</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73146; 108127</t>
+          <t>72307; 107990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71176; 96198</t>
+          <t>79288; 105282</t>
         </is>
       </c>
     </row>
